--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487431_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487431_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.848</v>
+        <v>2.4119</v>
       </c>
       <c r="E2" t="n">
-        <v>3.8108</v>
+        <v>3.4015</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.9628</v>
+        <v>-0.9896</v>
       </c>
       <c r="G2" t="n">
         <v>-0.08019999999999999</v>
@@ -610,13 +610,13 @@
         <v>1.5668</v>
       </c>
       <c r="S2" t="n">
-        <v>1.4831</v>
+        <v>1.047</v>
       </c>
       <c r="T2" t="n">
-        <v>1.3339</v>
+        <v>0.9245</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1492</v>
+        <v>0.1225</v>
       </c>
       <c r="V2" t="n">
         <v>-0.1217</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S. RAMOS DA CONCEIÇAO</t>
+          <t>A. SYTAR</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.1629</v>
+        <v>1.2735</v>
       </c>
       <c r="E3" t="n">
-        <v>3.4139</v>
+        <v>2.8932</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.2511</v>
+        <v>-1.6197</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.0237</v>
+        <v>-1.3891</v>
       </c>
       <c r="H3" t="n">
-        <v>0.33</v>
+        <v>-1.0001</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.3537</v>
+        <v>-0.3889</v>
       </c>
       <c r="J3" t="n">
-        <v>1.9324</v>
+        <v>2.0963</v>
       </c>
       <c r="K3" t="n">
-        <v>1.281</v>
+        <v>0.2227</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6515</v>
+        <v>1.8736</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.9562</v>
+        <v>-3.4853</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.951</v>
+        <v>-1.2228</v>
       </c>
       <c r="O3" t="n">
-        <v>-2.0052</v>
+        <v>-2.2625</v>
       </c>
       <c r="P3" t="n">
-        <v>1.1751</v>
+        <v>2.7419</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9792</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.1543</v>
+        <v>2.7419</v>
       </c>
       <c r="S3" t="n">
-        <v>2.4085</v>
+        <v>-0.9054</v>
       </c>
       <c r="T3" t="n">
-        <v>2.4607</v>
+        <v>-0.9127999999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0522</v>
+        <v>0.0074</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.397</v>
+        <v>0.8260999999999999</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.7097</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.397</v>
+        <v>-0.8837</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. SYTAR</t>
+          <t>S. RAMOS DA CONCEIÇAO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8198</v>
+        <v>0.6721</v>
       </c>
       <c r="E4" t="n">
-        <v>2.2792</v>
+        <v>2.0836</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.4594</v>
+        <v>-1.4114</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.3891</v>
+        <v>-1.0237</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.0001</v>
+        <v>0.33</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3889</v>
+        <v>-1.3537</v>
       </c>
       <c r="J4" t="n">
-        <v>2.0963</v>
+        <v>1.9324</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2227</v>
+        <v>1.281</v>
       </c>
       <c r="L4" t="n">
-        <v>1.8736</v>
+        <v>0.6515</v>
       </c>
       <c r="M4" t="n">
-        <v>-3.4853</v>
+        <v>-2.9562</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.2228</v>
+        <v>-0.951</v>
       </c>
       <c r="O4" t="n">
-        <v>-2.2625</v>
+        <v>-2.0052</v>
       </c>
       <c r="P4" t="n">
-        <v>2.7419</v>
+        <v>1.1751</v>
       </c>
       <c r="Q4" t="n">
+        <v>-0.9792</v>
+      </c>
+      <c r="R4" t="n">
+        <v>2.1543</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.9177999999999999</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.1304</v>
+      </c>
+      <c r="U4" t="n">
+        <v>-0.2126</v>
+      </c>
+      <c r="V4" t="n">
+        <v>-0.397</v>
+      </c>
+      <c r="W4" t="n">
         <v>0</v>
       </c>
-      <c r="R4" t="n">
-        <v>2.7419</v>
-      </c>
-      <c r="S4" t="n">
-        <v>-1.3591</v>
-      </c>
-      <c r="T4" t="n">
-        <v>-1.5268</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0.1677</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0.8260999999999999</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.7097</v>
-      </c>
       <c r="X4" t="n">
-        <v>-0.8837</v>
+        <v>-0.397</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2243</v>
+        <v>-0.67</v>
       </c>
       <c r="E5" t="n">
-        <v>1.1634</v>
+        <v>0.2424</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.9391</v>
+        <v>-0.9124</v>
       </c>
       <c r="G5" t="n">
         <v>-1.9881</v>
@@ -844,13 +844,13 @@
         <v>2.546</v>
       </c>
       <c r="S5" t="n">
-        <v>1.1382</v>
+        <v>0.2439</v>
       </c>
       <c r="T5" t="n">
-        <v>1.2021</v>
+        <v>0.2811</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0639</v>
+        <v>-0.0372</v>
       </c>
       <c r="V5" t="n">
         <v>0.4866</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.3753</v>
+        <v>-1.6543</v>
       </c>
       <c r="E6" t="n">
-        <v>-3.2652</v>
+        <v>-2.6512</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8899</v>
+        <v>0.9969</v>
       </c>
       <c r="G6" t="n">
         <v>-1.3368</v>
@@ -922,13 +922,13 @@
         <v>3.5253</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.3061</v>
+        <v>-0.5852000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.9634</v>
+        <v>-0.3494</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3428</v>
+        <v>-0.2358</v>
       </c>
       <c r="V6" t="n">
         <v>0.6594</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.6597</v>
+        <v>-2.798</v>
       </c>
       <c r="E7" t="n">
-        <v>-4.0201</v>
+        <v>-3.9177</v>
       </c>
       <c r="F7" t="n">
-        <v>1.3603</v>
+        <v>1.1198</v>
       </c>
       <c r="G7" t="n">
         <v>-0.8699</v>
@@ -1000,13 +1000,13 @@
         <v>3.1336</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3145</v>
+        <v>-0.4527</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.607</v>
+        <v>-0.5046</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2925</v>
+        <v>0.0519</v>
       </c>
       <c r="V7" t="n">
         <v>-1.6712</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-4.3609</v>
+        <v>-2.8923</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.6433</v>
+        <v>-0.4153</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.7176</v>
+        <v>-2.477</v>
       </c>
       <c r="G8" t="n">
         <v>-2.2187</v>
@@ -1078,13 +1078,13 @@
         <v>2.7419</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.8046</v>
+        <v>-0.336</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.1286</v>
+        <v>0.0994</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.6758999999999999</v>
+        <v>-0.4354</v>
       </c>
       <c r="V8" t="n">
         <v>-2.1003</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-6.8941</v>
+        <v>-6.5779</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.1142</v>
+        <v>-4.0119</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.7799</v>
+        <v>-2.566</v>
       </c>
       <c r="G9" t="n">
         <v>-5.327</v>
@@ -1156,13 +1156,13 @@
         <v>2.1543</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.763</v>
+        <v>-1.4468</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.9328</v>
+        <v>-0.8305</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.8302</v>
+        <v>-0.6163999999999999</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1192,16 +1192,16 @@
         <v>-10.235</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.375499999999999</v>
+        <v>-2.375399999999997</v>
       </c>
       <c r="F10" t="n">
-        <v>-7.859700000000002</v>
+        <v>-7.859399999999999</v>
       </c>
       <c r="G10" t="n">
         <v>-14.2335</v>
       </c>
       <c r="H10" t="n">
-        <v>-6.150600000000001</v>
+        <v>-6.1506</v>
       </c>
       <c r="I10" t="n">
         <v>-8.082899999999999</v>
@@ -1213,7 +1213,7 @@
         <v>4.7237</v>
       </c>
       <c r="L10" t="n">
-        <v>1.157</v>
+        <v>1.157000000000001</v>
       </c>
       <c r="M10" t="n">
         <v>-20.1141</v>
@@ -1222,7 +1222,7 @@
         <v>-10.8741</v>
       </c>
       <c r="O10" t="n">
-        <v>-9.239899999999999</v>
+        <v>-9.2399</v>
       </c>
       <c r="P10" t="n">
         <v>7.8338</v>
@@ -1234,10 +1234,10 @@
         <v>20.5641</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.5175</v>
+        <v>-1.517400000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1619000000000002</v>
+        <v>-0.1618999999999999</v>
       </c>
       <c r="U10" t="n">
         <v>-1.3556</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>K. FALL</t>
+          <t>R. ESPINOZA OROZCO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>5.2055</v>
+        <v>5.4141</v>
       </c>
       <c r="E11" t="n">
-        <v>3.4524</v>
+        <v>4.0298</v>
       </c>
       <c r="F11" t="n">
-        <v>1.7532</v>
+        <v>1.3843</v>
       </c>
       <c r="G11" t="n">
-        <v>4.283</v>
+        <v>-0.0289</v>
       </c>
       <c r="H11" t="n">
-        <v>4.0905</v>
+        <v>-1.8676</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1924</v>
+        <v>1.8387</v>
       </c>
       <c r="J11" t="n">
-        <v>5.6038</v>
+        <v>0.7441</v>
       </c>
       <c r="K11" t="n">
-        <v>4.629</v>
+        <v>-1.0582</v>
       </c>
       <c r="L11" t="n">
-        <v>0.9748</v>
+        <v>1.8024</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.3209</v>
+        <v>-0.773</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.5385</v>
+        <v>-0.8093</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.7823</v>
+        <v>0.0363</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.546</v>
+        <v>0.5875</v>
       </c>
       <c r="Q11" t="n">
-        <v>-4.8962</v>
+        <v>-1.9585</v>
       </c>
       <c r="R11" t="n">
-        <v>2.3502</v>
+        <v>2.546</v>
       </c>
       <c r="S11" t="n">
-        <v>1.9767</v>
+        <v>0.0466</v>
       </c>
       <c r="T11" t="n">
-        <v>0.9775</v>
+        <v>0.16</v>
       </c>
       <c r="U11" t="n">
-        <v>0.9992</v>
+        <v>-0.1134</v>
       </c>
       <c r="V11" t="n">
-        <v>1.492</v>
+        <v>4.8088</v>
       </c>
       <c r="W11" t="n">
-        <v>1.7673</v>
+        <v>5.0842</v>
       </c>
       <c r="X11" t="n">
         <v>-0.2754</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>R. ESPINOZA OROZCO</t>
+          <t>K. FALL</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,64 +1345,64 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>4.9882</v>
+        <v>4.5409</v>
       </c>
       <c r="E12" t="n">
-        <v>3.9274</v>
+        <v>2.8384</v>
       </c>
       <c r="F12" t="n">
-        <v>1.0608</v>
+        <v>1.7025</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.0289</v>
+        <v>4.283</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.8676</v>
+        <v>4.0905</v>
       </c>
       <c r="I12" t="n">
-        <v>1.8387</v>
+        <v>0.1924</v>
       </c>
       <c r="J12" t="n">
-        <v>0.7441</v>
+        <v>5.6038</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.0582</v>
+        <v>4.629</v>
       </c>
       <c r="L12" t="n">
-        <v>1.8024</v>
+        <v>0.9748</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.773</v>
+        <v>-1.3209</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.8093</v>
+        <v>-0.5385</v>
       </c>
       <c r="O12" t="n">
-        <v>0.0363</v>
+        <v>-0.7823</v>
       </c>
       <c r="P12" t="n">
-        <v>0.5875</v>
+        <v>-2.546</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.9585</v>
+        <v>-4.8962</v>
       </c>
       <c r="R12" t="n">
-        <v>2.546</v>
+        <v>2.3502</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3793</v>
+        <v>1.312</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0576</v>
+        <v>0.3635</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4369</v>
+        <v>0.9485</v>
       </c>
       <c r="V12" t="n">
-        <v>4.8088</v>
+        <v>1.492</v>
       </c>
       <c r="W12" t="n">
-        <v>5.0842</v>
+        <v>1.7673</v>
       </c>
       <c r="X12" t="n">
         <v>-0.2754</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.0614</v>
+        <v>4.22</v>
       </c>
       <c r="E13" t="n">
-        <v>3.8158</v>
+        <v>3.9182</v>
       </c>
       <c r="F13" t="n">
-        <v>0.2456</v>
+        <v>0.3019</v>
       </c>
       <c r="G13" t="n">
         <v>6.6917</v>
@@ -1468,13 +1468,13 @@
         <v>2.3502</v>
       </c>
       <c r="S13" t="n">
-        <v>0.9146</v>
+        <v>1.0732</v>
       </c>
       <c r="T13" t="n">
-        <v>0.414</v>
+        <v>0.5164</v>
       </c>
       <c r="U13" t="n">
-        <v>0.5006</v>
+        <v>0.5568</v>
       </c>
       <c r="V13" t="n">
         <v>-0.9988</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.3005</v>
+        <v>1.8728</v>
       </c>
       <c r="E14" t="n">
         <v>1.2348</v>
       </c>
       <c r="F14" t="n">
-        <v>1.0657</v>
+        <v>0.638</v>
       </c>
       <c r="G14" t="n">
         <v>1.4322</v>
@@ -1546,13 +1546,13 @@
         <v>0.3917</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1436</v>
+        <v>-0.2841</v>
       </c>
       <c r="T14" t="n">
         <v>0.1476</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.004</v>
+        <v>-0.4317</v>
       </c>
       <c r="V14" t="n">
         <v>0.3329</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>F. VIDAL PATIÑO</t>
+          <t>J. MARTINEZ FERREIRO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0225</v>
+        <v>0.215</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.6942</v>
+        <v>1.3284</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7167</v>
+        <v>-1.1134</v>
       </c>
       <c r="G15" t="n">
-        <v>1.9329</v>
+        <v>0.7727000000000001</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9422</v>
+        <v>-0.4546</v>
       </c>
       <c r="I15" t="n">
-        <v>0.9907</v>
+        <v>1.2273</v>
       </c>
       <c r="J15" t="n">
-        <v>1.5091</v>
+        <v>1.2425</v>
       </c>
       <c r="K15" t="n">
-        <v>1.3474</v>
+        <v>0.0204</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1617</v>
+        <v>1.2221</v>
       </c>
       <c r="M15" t="n">
-        <v>0.4239</v>
+        <v>-0.4698</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.4052</v>
+        <v>-0.475</v>
       </c>
       <c r="O15" t="n">
-        <v>0.8290999999999999</v>
+        <v>0.0052</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.3709</v>
+        <v>0.1958</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.9585</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.5875</v>
+        <v>0.1958</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.5395</v>
+        <v>-0.1453</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0882</v>
+        <v>0.0859</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.6277</v>
+        <v>-0.2311</v>
       </c>
       <c r="V15" t="n">
+        <v>-0.6083</v>
+      </c>
+      <c r="W15" t="n">
         <v>0</v>
       </c>
-      <c r="W15" t="n">
-        <v>-0.3329</v>
-      </c>
       <c r="X15" t="n">
-        <v>0.3329</v>
+        <v>-0.6083</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. MARTINEZ FERREIRO</t>
+          <t>F. VIDAL PATIÑO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.09660000000000001</v>
+        <v>-0.3112</v>
       </c>
       <c r="E16" t="n">
-        <v>1.1237</v>
+        <v>-1.0012</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.2203</v>
+        <v>0.6899</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7727000000000001</v>
+        <v>1.9329</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.4546</v>
+        <v>0.9422</v>
       </c>
       <c r="I16" t="n">
-        <v>1.2273</v>
+        <v>0.9907</v>
       </c>
       <c r="J16" t="n">
-        <v>1.2425</v>
+        <v>1.5091</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0204</v>
+        <v>1.3474</v>
       </c>
       <c r="L16" t="n">
-        <v>1.2221</v>
+        <v>0.1617</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.4698</v>
+        <v>0.4239</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.475</v>
+        <v>-0.4052</v>
       </c>
       <c r="O16" t="n">
-        <v>0.0052</v>
+        <v>0.8290999999999999</v>
       </c>
       <c r="P16" t="n">
-        <v>0.1958</v>
+        <v>-1.3709</v>
       </c>
       <c r="Q16" t="n">
+        <v>-1.9585</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.5875</v>
+      </c>
+      <c r="S16" t="n">
+        <v>-0.8732</v>
+      </c>
+      <c r="T16" t="n">
+        <v>-0.2188</v>
+      </c>
+      <c r="U16" t="n">
+        <v>-0.6544</v>
+      </c>
+      <c r="V16" t="n">
         <v>0</v>
       </c>
-      <c r="R16" t="n">
-        <v>0.1958</v>
-      </c>
-      <c r="S16" t="n">
-        <v>-0.4569</v>
-      </c>
-      <c r="T16" t="n">
-        <v>-0.1188</v>
-      </c>
-      <c r="U16" t="n">
-        <v>-0.3381</v>
-      </c>
-      <c r="V16" t="n">
-        <v>-0.6083</v>
-      </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>-0.3329</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.6083</v>
+        <v>0.3329</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X. QUINTELA VALCARCEL</t>
+          <t>A. CORBACHO DE LA CRUZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.7313</v>
+        <v>-0.3751</v>
       </c>
       <c r="E17" t="n">
-        <v>1.9188</v>
+        <v>-2.4631</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.6501</v>
+        <v>2.088</v>
       </c>
       <c r="G17" t="n">
-        <v>3.5129</v>
+        <v>-3.9314</v>
       </c>
       <c r="H17" t="n">
-        <v>1.5074</v>
+        <v>-0.1108</v>
       </c>
       <c r="I17" t="n">
-        <v>2.0056</v>
+        <v>-3.8205</v>
       </c>
       <c r="J17" t="n">
-        <v>5.591</v>
+        <v>-3.2126</v>
       </c>
       <c r="K17" t="n">
-        <v>2.3886</v>
+        <v>0.2246</v>
       </c>
       <c r="L17" t="n">
-        <v>3.2024</v>
+        <v>-3.4371</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.0781</v>
+        <v>-0.7188</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.8812</v>
+        <v>-0.3354</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.1969</v>
+        <v>-0.3834</v>
       </c>
       <c r="P17" t="n">
-        <v>-2.9377</v>
+        <v>1.7626</v>
       </c>
       <c r="Q17" t="n">
-        <v>-4.8962</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.9585</v>
+        <v>1.7626</v>
       </c>
       <c r="S17" t="n">
-        <v>0.243</v>
+        <v>1.1278</v>
       </c>
       <c r="T17" t="n">
-        <v>0.9487</v>
+        <v>0.1411</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.7056</v>
+        <v>0.9866</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.5495</v>
+        <v>0.6659</v>
       </c>
       <c r="W17" t="n">
-        <v>0.2754</v>
+        <v>0.6083</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.8249</v>
+        <v>0.0576</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. CORBACHO DE LA CRUZ</t>
+          <t>X. QUINTELA VALCARCEL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.8673999999999999</v>
+        <v>-0.4253</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.8725</v>
+        <v>1.7141</v>
       </c>
       <c r="F18" t="n">
-        <v>2.0051</v>
+        <v>-2.1394</v>
       </c>
       <c r="G18" t="n">
-        <v>-3.9314</v>
+        <v>3.5129</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.1108</v>
+        <v>1.5074</v>
       </c>
       <c r="I18" t="n">
-        <v>-3.8205</v>
+        <v>2.0056</v>
       </c>
       <c r="J18" t="n">
-        <v>-3.2126</v>
+        <v>5.591</v>
       </c>
       <c r="K18" t="n">
-        <v>0.2246</v>
+        <v>2.3886</v>
       </c>
       <c r="L18" t="n">
-        <v>-3.4371</v>
+        <v>3.2024</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.7188</v>
+        <v>-2.0781</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.3354</v>
+        <v>-0.8812</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.3834</v>
+        <v>-1.1969</v>
       </c>
       <c r="P18" t="n">
-        <v>1.7626</v>
+        <v>-2.9377</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-4.8962</v>
       </c>
       <c r="R18" t="n">
-        <v>1.7626</v>
+        <v>1.9585</v>
       </c>
       <c r="S18" t="n">
-        <v>0.6354</v>
+        <v>0.549</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2682</v>
+        <v>0.744</v>
       </c>
       <c r="U18" t="n">
-        <v>0.9036</v>
+        <v>-0.195</v>
       </c>
       <c r="V18" t="n">
-        <v>0.6659</v>
+        <v>-1.5495</v>
       </c>
       <c r="W18" t="n">
-        <v>0.6083</v>
+        <v>0.2754</v>
       </c>
       <c r="X18" t="n">
-        <v>0.0576</v>
+        <v>-1.8249</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-4.6478</v>
+        <v>-4.2339</v>
       </c>
       <c r="E19" t="n">
-        <v>-4.0467</v>
+        <v>-3.7397</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.6011</v>
+        <v>-0.4942</v>
       </c>
       <c r="G19" t="n">
         <v>-0.4316</v>
@@ -1936,13 +1936,13 @@
         <v>0.5875</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.0203</v>
+        <v>-0.6064000000000001</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.891</v>
+        <v>-0.584</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1293</v>
+        <v>-0.0223</v>
       </c>
       <c r="V19" t="n">
         <v>-1.8249</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>10.235</v>
+        <v>10.9173</v>
       </c>
       <c r="E20" t="n">
-        <v>7.859499999999998</v>
+        <v>7.859700000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>2.3756</v>
+        <v>3.0576</v>
       </c>
       <c r="G20" t="n">
         <v>14.2335</v>
@@ -2014,13 +2014,13 @@
         <v>12.73</v>
       </c>
       <c r="S20" t="n">
-        <v>1.5173</v>
+        <v>2.1996</v>
       </c>
       <c r="T20" t="n">
-        <v>1.3556</v>
+        <v>1.3557</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1617999999999999</v>
+        <v>0.8440000000000001</v>
       </c>
       <c r="V20" t="n">
         <v>2.3181</v>
